--- a/02/020_practice_sales.xlsx
+++ b/02/020_practice_sales.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="1" r:id="R9dfc6408d5354881"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="販売記録" sheetId="2" r:id="R97b7f40574134ee3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="集計チャレンジ" sheetId="3" r:id="R71f90332d89e49ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品マスタ" sheetId="4" r:id="Rbbefda5db7cc475e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="答え合わせ" sheetId="5" r:id="R0abd47f741234056"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使い方" sheetId="1" r:id="Rcb335c84a2ab410a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="販売記録" sheetId="2" r:id="Rc1c4cb36be6f4ad3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="集計チャレンジ" sheetId="3" r:id="Rab0af6c26477437c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="商品マスタ" sheetId="4" r:id="R92776a72bb714f39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="答え合わせ" sheetId="5" r:id="R0a2336785389438f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -755,7 +755,7 @@
         <x:color rgb="FFB83A4B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF0F2"/>
         </x:patternFill>
       </x:fill>
@@ -900,7 +900,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R93e86cdad0134a7a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R924c0f246c6b41ba"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1308,7 +1308,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B11" s="46" t="str">
-        <x:v>集計チャレンジ!B5:B8 と B13:B16 に集計式を作る</x:v>
+        <x:v>集計チャレンジ!B5:B8 と B12:B16 に集計式を作る</x:v>
       </x:c>
       <x:c r="C11" s="38"/>
       <x:c r="D11" s="38"/>
@@ -2134,9 +2134,9 @@
     <x:mergeCell ref="A1:J2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R160f44075b0746a7"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39d9af3cbe224449"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8f57cc0042548c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reca7ef10f5bd4fae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3407,6 +3407,6 @@
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="要確認"/>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7c78811259d458e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd45102146988424b"/>
 </x:worksheet>
 </file>